--- a/naver-place-crawler/results_hair/북구_미용실.xlsx
+++ b/naver-place-crawler/results_hair/북구_미용실.xlsx
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="Q3" t="n">
         <v>254</v>
       </c>
       <c r="R3" t="n">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4215</v>
+        <v>4216</v>
       </c>
       <c r="Q9" t="n">
         <v>195</v>
       </c>
       <c r="R9" t="n">
-        <v>4410</v>
+        <v>4411</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mukbbo__o@naver.com</t>
+          <t>bomi0306@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ouou1771@naver.com</t>
+          <t>korea20027@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -5607,13 +5607,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>7871</v>
+        <v>7872</v>
       </c>
       <c r="Q55" t="n">
         <v>147</v>
       </c>
       <c r="R55" t="n">
-        <v>8018</v>
+        <v>8019</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_hair/북구_미용실.xlsx
+++ b/naver-place-crawler/results_hair/북구_미용실.xlsx
@@ -564,39 +564,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>헤어 피어나다</t>
+          <t>쿤스트헤어</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>forhr85@naver.com</t>
+          <t>302591@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1475-0557</t>
+          <t>0507-1375-0309</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대학로 59 1층 헤어피어나다</t>
+          <t>대구광역시 북구 칠곡중앙대로69길 7 1층 쿤스트헤어</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/forhr85</t>
+          <t>https://m.place.naver.com/hairshop/1212188634/stylist?theme=place&amp;entry=pll&amp;lang=ko</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wsu107k</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2440</v>
+        <v>371</v>
       </c>
       <c r="Q2" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>2512</v>
+        <v>378</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1402995647</t>
+          <t>1212188634</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1402995647</t>
+          <t>https://m.place.naver.com/place/1212188634</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>유키니언 25호 대구침산점</t>
+          <t>헤어 피어나다</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>thssksfh12@naver.com</t>
+          <t>forhr85@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1419-7026</t>
+          <t>0507-1475-0557</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대구광역시 북구 호암로 6 2층 유키니언 25호 대구침산점</t>
+          <t>대구광역시 북구 대학로 59 1층 헤어피어나다</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yuki_chimsan</t>
+          <t>https://blog.naver.com/forhr85</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -711,17 +715,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1442</v>
+        <v>2440</v>
       </c>
       <c r="Q3" t="n">
-        <v>254</v>
+        <v>72</v>
       </c>
       <c r="R3" t="n">
-        <v>1696</v>
+        <v>2512</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1799226004</t>
+          <t>1402995647</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1799226004</t>
+          <t>https://m.place.naver.com/place/1402995647</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>더화사헤어침산점</t>
+          <t>유키니언 25호 대구침산점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kwak4534@naver.com</t>
+          <t>thssksfh12@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1373-5335</t>
+          <t>0507-1419-7026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로31길 32 2층 더화사헤어</t>
+          <t>대구광역시 북구 호암로 6 2층 유키니언 25호 대구침산점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/yuki_chimsan</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,7 +788,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -805,17 +809,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>745</v>
+        <v>1442</v>
       </c>
       <c r="Q4" t="n">
-        <v>94</v>
+        <v>254</v>
       </c>
       <c r="R4" t="n">
-        <v>839</v>
+        <v>1696</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1376844921</t>
+          <t>1799226004</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1376844921</t>
+          <t>https://m.place.naver.com/place/1799226004</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,38 +850,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>헤어하리</t>
+          <t>더화사헤어침산점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>hairhari@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>cto@handsos.com</t>
-        </is>
-      </c>
+          <t>kwak4534@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1436-0342</t>
+          <t>0507-1373-5335</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 439 3층 헤어하리</t>
+          <t>대구광역시 북구 침산남로31길 32 2층 더화사헤어</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/791322</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1896</v>
+        <v>745</v>
       </c>
       <c r="Q5" t="n">
-        <v>288</v>
+        <v>94</v>
       </c>
       <c r="R5" t="n">
-        <v>2184</v>
+        <v>839</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,12 +922,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1844168743</t>
+          <t>1376844921</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1844168743</t>
+          <t>https://m.place.naver.com/place/1376844921</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -944,29 +944,33 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>일이헤어</t>
+          <t>헤어하리</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1211air@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>hairhari@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>cto@handsos.com</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1446-0909</t>
+          <t>0507-1436-0342</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구광역시 북구 경진로1길 29 1층</t>
+          <t>대구광역시 북구 학정로 439 3층 헤어하리</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bokguman_official</t>
+          <t>https://booking.naver.com/booking/13/bizes/791322</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -976,12 +980,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1001,13 +1005,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>464</v>
+        <v>1896</v>
       </c>
       <c r="Q6" t="n">
-        <v>163</v>
+        <v>288</v>
       </c>
       <c r="R6" t="n">
-        <v>627</v>
+        <v>2184</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,12 +1020,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1879258800</t>
+          <t>1844168743</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1879258800</t>
+          <t>https://m.place.naver.com/place/1844168743</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1038,29 +1042,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The감동hair</t>
+          <t>일이헤어</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>thegamdong_49@naver.com</t>
+          <t>1211air@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1430-7024</t>
+          <t>0507-1446-0909</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 80 상가동 1층 107호</t>
+          <t>대구광역시 북구 경진로1길 29 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thegamdong_49</t>
+          <t>https://www.instagram.com/bokguman_official</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1075,7 +1079,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,17 +1095,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>166</v>
+        <v>464</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>163</v>
       </c>
       <c r="R7" t="n">
-        <v>173</v>
+        <v>627</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1114,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1664790035</t>
+          <t>1879258800</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1664790035</t>
+          <t>https://m.place.naver.com/place/1879258800</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1132,29 +1136,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>언와인드헤어</t>
+          <t>The감동hair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>xssm12@naver.com</t>
+          <t>thegamdong_49@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1388-0458</t>
+          <t>0507-1430-7024</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구광역시 북구 구암로 137 2층</t>
+          <t>대구광역시 북구 침산남로 80 상가동 1층 107호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/unwind_jumi?igsh=ajB3NnVndzR2ODN2&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/thegamdong_49</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1169,7 +1173,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1185,17 +1189,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="Q8" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1208,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2033155374</t>
+          <t>1664790035</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2033155374</t>
+          <t>https://m.place.naver.com/place/1664790035</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1226,29 +1230,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>크리우헤어 침산점</t>
+          <t>언와인드헤어</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>us990@naver.com</t>
+          <t>xssm12@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1495-7768</t>
+          <t>0507-1388-0458</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 100 상가동 1층 116, 117, 118호</t>
+          <t>대구광역시 북구 구암로 137 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/criw._love</t>
+          <t>https://www.instagram.com/unwind_jumi?igsh=ajB3NnVndzR2ODN2&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,13 +1287,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4216</v>
+        <v>154</v>
       </c>
       <c r="Q9" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="R9" t="n">
-        <v>4411</v>
+        <v>177</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1302,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1303406245</t>
+          <t>2033155374</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1303406245</t>
+          <t>https://m.place.naver.com/place/2033155374</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1320,29 +1324,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>바오헤어</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>bao1211-1@naver.com</t>
-        </is>
-      </c>
+          <t>크리우헤어 침산점</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1341-1239</t>
+          <t>0507-1495-7768</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구광역시 북구 도남중앙로7길 2 골드드림타워 2층</t>
+          <t>대구광역시 북구 침산로 100 상가동 1층 116, 117, 118호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bao1211-1</t>
+          <t>https://www.instagram.com/criw._love</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1381</v>
+        <v>4216</v>
       </c>
       <c r="Q10" t="n">
-        <v>254</v>
+        <v>195</v>
       </c>
       <c r="R10" t="n">
-        <v>1635</v>
+        <v>4411</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1021729399</t>
+          <t>1303406245</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1021729399</t>
+          <t>https://m.place.naver.com/place/1303406245</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1414,29 +1414,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>집앞미용실</t>
+          <t>바오헤어</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ekdms2373@naver.com</t>
+          <t>bao1211-1@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1372-8457</t>
+          <t>0507-1341-1239</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구광역시 북구 구암로49길 27</t>
+          <t>대구광역시 북구 도남중앙로7길 2 골드드림타워 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jib_ap_hair/</t>
+          <t>https://blog.naver.com/bao1211-1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1471,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>472</v>
+        <v>1382</v>
       </c>
       <c r="Q11" t="n">
-        <v>40</v>
+        <v>254</v>
       </c>
       <c r="R11" t="n">
-        <v>512</v>
+        <v>1636</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1096726564</t>
+          <t>1021729399</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1096726564</t>
+          <t>https://m.place.naver.com/place/1021729399</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1508,29 +1508,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>모먼트헤어</t>
+          <t>집앞미용실</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>momenthair-@naver.com</t>
+          <t>ekdms2373@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1483-8000</t>
+          <t>0507-1372-8457</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 415 2층 201호</t>
+          <t>대구광역시 북구 구암로49길 27</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_moment_hair</t>
+          <t>https://www.instagram.com/jib_ap_hair/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>78</v>
+        <v>472</v>
       </c>
       <c r="Q12" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="R12" t="n">
-        <v>90</v>
+        <v>512</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2067037578</t>
+          <t>1096726564</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2067037578</t>
+          <t>https://m.place.naver.com/place/1096726564</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1602,29 +1602,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>신정헤어라인 동천점</t>
+          <t>모먼트헤어</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>love_hcjh@naver.com</t>
+          <t>momenthair-@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1339-2771</t>
+          <t>0507-1483-8000</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로 127 2층 신정헤어라인 동천점</t>
+          <t>대구광역시 북구 학정로 415 2층 201호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/_moment_hair</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1655,17 +1655,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>725</v>
+        <v>78</v>
       </c>
       <c r="Q13" t="n">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="R13" t="n">
-        <v>776</v>
+        <v>90</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>16081732</t>
+          <t>2067037578</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16081732</t>
+          <t>https://m.place.naver.com/place/2067037578</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1696,29 +1696,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>유이스트</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>miso-so11@naver.com</t>
-        </is>
-      </c>
+          <t>신정헤어라인 동천점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1346-5534</t>
+          <t>0507-1339-2771</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로21길 23 103동 2층상가 유이스트</t>
+          <t>대구광역시 북구 동천로 127 2층 신정헤어라인 동천점</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yuist_miso</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1728,7 +1724,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1749,17 +1745,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3973</v>
+        <v>725</v>
       </c>
       <c r="Q14" t="n">
-        <v>250</v>
+        <v>51</v>
       </c>
       <c r="R14" t="n">
-        <v>4223</v>
+        <v>776</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1768,12 +1764,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1571901409</t>
+          <t>16081732</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1571901409</t>
+          <t>https://m.place.naver.com/place/16081732</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1790,29 +1786,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>오보에 침산점</t>
+          <t>유이스트</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>seouna917@naver.com</t>
+          <t>miso-so11@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1446-7771</t>
+          <t>0507-1346-5534</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로32길 10 1동 102호</t>
+          <t>대구광역시 북구 침산로21길 23 103동 2층상가 유이스트</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ovoe_unaa</t>
+          <t>https://www.instagram.com/yuist_miso</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1847,13 +1843,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2317</v>
+        <v>3973</v>
       </c>
       <c r="Q15" t="n">
-        <v>102</v>
+        <v>250</v>
       </c>
       <c r="R15" t="n">
-        <v>2419</v>
+        <v>4223</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1862,12 +1858,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1968509465</t>
+          <t>1571901409</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1968509465</t>
+          <t>https://m.place.naver.com/place/1571901409</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1884,29 +1880,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>라벨르</t>
+          <t>오보에 침산점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>labelle0322@naver.com</t>
+          <t>seouna917@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1353-4510</t>
+          <t>0507-1446-7771</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로23길 2 3층 라벨르</t>
+          <t>대구광역시 북구 침산남로32길 10 1동 102호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/ovoe_unaa</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1916,7 +1912,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1937,17 +1933,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>465</v>
+        <v>2318</v>
       </c>
       <c r="Q16" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="R16" t="n">
-        <v>570</v>
+        <v>2420</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1956,12 +1952,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1321918720</t>
+          <t>1968509465</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1321918720</t>
+          <t>https://m.place.naver.com/place/1968509465</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1978,29 +1974,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>디옴므헤어</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>eodud0850@naver.com</t>
-        </is>
-      </c>
+          <t>라벨르</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1467-0750</t>
+          <t>0507-1353-4510</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>대구광역시 북구 도남중앙로7길 6 202호</t>
+          <t>대구광역시 북구 동천로23길 2 3층 라벨르</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/d.homme_hair?igsh=MTJrZWJjYzcya2o2bw%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2010,7 +2002,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2031,17 +2023,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="Q17" t="n">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="R17" t="n">
-        <v>526</v>
+        <v>571</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2050,12 +2042,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1275438401</t>
+          <t>1321918720</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1275438401</t>
+          <t>https://m.place.naver.com/place/1321918720</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2072,29 +2064,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>지니헤어 연경점</t>
+          <t>디옴므헤어</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>jinihair_@naver.com</t>
+          <t>eodud0850@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1469-1352</t>
+          <t>0507-1467-0750</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>대구광역시 북구 연경중앙로 11 백조예미지상가105호</t>
+          <t>대구광역시 북구 도남중앙로7길 6 202호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>http://instagram.com/jinihair_jin</t>
+          <t>https://www.instagram.com/d.homme_hair?igsh=MTJrZWJjYzcya2o2bw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2129,13 +2121,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>549</v>
+        <v>469</v>
       </c>
       <c r="Q18" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="R18" t="n">
-        <v>622</v>
+        <v>526</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2144,12 +2136,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1552155123</t>
+          <t>1275438401</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1552155123</t>
+          <t>https://m.place.naver.com/place/1275438401</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2166,29 +2158,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S석용오헤어</t>
+          <t>지니헤어 연경점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>days0426@naver.com</t>
+          <t>jinihair_@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1365-9627</t>
+          <t>0507-1469-1352</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 269</t>
+          <t>대구광역시 북구 연경중앙로 11 백조예미지상가105호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/jinihair_jin</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2198,7 +2190,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2219,17 +2211,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>462</v>
+        <v>549</v>
       </c>
       <c r="Q19" t="n">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="R19" t="n">
-        <v>474</v>
+        <v>622</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2238,12 +2230,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>36449643</t>
+          <t>1552155123</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36449643</t>
+          <t>https://m.place.naver.com/place/1552155123</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2260,29 +2252,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>마일드헤어</t>
+          <t>S석용오헤어</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>mildh1223@naver.com</t>
+          <t>days0426@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>053-939-1048</t>
+          <t>0507-1365-9627</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대현로 74 비앤비빌딩2층 마일드헤어</t>
+          <t>대구광역시 북구 동북로 269</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mildh1223</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2292,12 +2284,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2313,17 +2305,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2311</v>
+        <v>462</v>
       </c>
       <c r="Q20" t="n">
-        <v>561</v>
+        <v>12</v>
       </c>
       <c r="R20" t="n">
-        <v>2872</v>
+        <v>474</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2332,12 +2324,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1579426055</t>
+          <t>36449643</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1579426055</t>
+          <t>https://m.place.naver.com/place/36449643</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2354,29 +2346,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>아이드블랑 칠곡점</t>
+          <t>마일드헤어</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>mzmz0903@naver.com</t>
+          <t>mildh1223@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1421-0810</t>
+          <t>053-939-1048</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>대구광역시 북구 구암로65길 52 2층 아이드블랑</t>
+          <t>대구광역시 북구 대현로 74 비앤비빌딩2층 마일드헤어</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mzmz0903</t>
+          <t>https://blog.naver.com/mildh1223</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2407,17 +2399,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>5435</v>
+        <v>2311</v>
       </c>
       <c r="Q21" t="n">
-        <v>68</v>
+        <v>561</v>
       </c>
       <c r="R21" t="n">
-        <v>5503</v>
+        <v>2872</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2426,12 +2418,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1138937832</t>
+          <t>1579426055</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138937832</t>
+          <t>https://m.place.naver.com/place/1579426055</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2448,29 +2440,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>이메진스튜디오</t>
+          <t>아이드블랑 칠곡점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>sarara_77@naver.com</t>
+          <t>mzmz0903@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1325-1116</t>
+          <t>0507-1421-0810</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 247 이편한세상복현 상가동 2층 201호</t>
+          <t>대구광역시 북구 구암로65길 52 2층 아이드블랑</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://instagram.com/im_st_sarah</t>
+          <t>https://blog.naver.com/mzmz0903</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2485,7 +2477,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2501,17 +2493,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2004</v>
+        <v>5436</v>
       </c>
       <c r="Q22" t="n">
-        <v>226</v>
+        <v>68</v>
       </c>
       <c r="R22" t="n">
-        <v>2230</v>
+        <v>5504</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2520,12 +2512,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1641409682</t>
+          <t>1138937832</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1641409682</t>
+          <t>https://m.place.naver.com/place/1138937832</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2542,29 +2534,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>글이헤어</t>
+          <t>이메진스튜디오</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>bling44@naver.com</t>
+          <t>sarara_77@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1334-9931</t>
+          <t>0507-1325-1116</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로서37길 4 리치하임 1층 글이헤어</t>
+          <t>대구광역시 북구 동북로 247 이편한세상복현 상가동 2층 201호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dm1203ab</t>
+          <t>https://instagram.com/im_st_sarah</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2599,13 +2591,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>711</v>
+        <v>2004</v>
       </c>
       <c r="Q23" t="n">
-        <v>62</v>
+        <v>226</v>
       </c>
       <c r="R23" t="n">
-        <v>773</v>
+        <v>2230</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2614,12 +2606,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1744521773</t>
+          <t>1641409682</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1744521773</t>
+          <t>https://m.place.naver.com/place/1641409682</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2636,29 +2628,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>오레아 헤어</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>0rea_hair@naver.com</t>
-        </is>
-      </c>
+          <t>글이헤어</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1449-2575</t>
+          <t>0507-1334-9931</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>대구광역시 북구 태전로3길 17 1층</t>
+          <t>대구광역시 북구 동북로서37길 4 리치하임 1층 글이헤어</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/0rea_hair</t>
+          <t>https://www.instagram.com/dm1203ab</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2673,7 +2661,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2693,13 +2681,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>129</v>
+        <v>711</v>
       </c>
       <c r="Q24" t="n">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="R24" t="n">
-        <v>136</v>
+        <v>773</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2708,12 +2696,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2050337551</t>
+          <t>1744521773</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2050337551</t>
+          <t>https://m.place.naver.com/place/1744521773</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2730,29 +2718,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>파마중</t>
+          <t>오레아 헤어</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>wjdcjdtla@naver.com</t>
+          <t>0rea_hair@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>053-321-7779</t>
+          <t>0507-1449-2575</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로 450 1층 112호 파마중</t>
+          <t>대구광역시 북구 태전로3길 17 1층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wjdcjdtla</t>
+          <t>https://blog.naver.com/0rea_hair</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2787,13 +2775,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>666</v>
+        <v>129</v>
       </c>
       <c r="Q25" t="n">
-        <v>312</v>
+        <v>7</v>
       </c>
       <c r="R25" t="n">
-        <v>978</v>
+        <v>136</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2802,12 +2790,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1210183889</t>
+          <t>2050337551</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1210183889</t>
+          <t>https://m.place.naver.com/place/2050337551</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2824,29 +2812,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>온데아르헤어 산격점</t>
+          <t>파마중</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ondear_hair@naver.com</t>
+          <t>wjdcjdtla@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1478-7898</t>
+          <t>053-321-7779</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대학로23길 7-2 온데아르헤어</t>
+          <t>대구광역시 북구 칠곡중앙대로 450 1층 112호 파마중</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ondear_hair</t>
+          <t>https://blog.naver.com/wjdcjdtla</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2881,13 +2869,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>741</v>
+        <v>666</v>
       </c>
       <c r="Q26" t="n">
-        <v>34</v>
+        <v>312</v>
       </c>
       <c r="R26" t="n">
-        <v>775</v>
+        <v>978</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2896,12 +2884,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1503636560</t>
+          <t>1210183889</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1503636560</t>
+          <t>https://m.place.naver.com/place/1210183889</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2918,29 +2906,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>부헤어스토리</t>
+          <t>온데아르헤어 산격점</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mama8820@naver.com</t>
+          <t>ondear_hair@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1304-8616</t>
+          <t>0507-1478-7898</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 426 2층 부헤어</t>
+          <t>대구광역시 북구 대학로23길 7-2 온데아르헤어</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>http://instagram.com/boohair_ok</t>
+          <t>https://blog.naver.com/ondear_hair</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2955,7 +2943,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2975,13 +2963,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2031</v>
+        <v>741</v>
       </c>
       <c r="Q27" t="n">
-        <v>192</v>
+        <v>34</v>
       </c>
       <c r="R27" t="n">
-        <v>2223</v>
+        <v>775</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2990,12 +2978,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1753422125</t>
+          <t>1503636560</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1753422125</t>
+          <t>https://m.place.naver.com/place/1503636560</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3012,29 +3000,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>어레브헤어 대구 고성점</t>
+          <t>부헤어스토리</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>golbange83@naver.com</t>
+          <t>mama8820@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1371-2389</t>
+          <t>0507-1304-8616</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>대구광역시 북구 고성로34길 69 1층 어레브헤어 대구 고성점</t>
+          <t>대구광역시 북구 학정로 426 2층 부헤어</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/golbange83</t>
+          <t>http://instagram.com/boohair_ok</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3049,7 +3037,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3069,13 +3057,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1940</v>
+        <v>2031</v>
       </c>
       <c r="Q28" t="n">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="R28" t="n">
-        <v>2163</v>
+        <v>2223</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3084,12 +3072,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1768754785</t>
+          <t>1753422125</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1768754785</t>
+          <t>https://m.place.naver.com/place/1753422125</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3106,29 +3094,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>설헤어</t>
+          <t>어레브헤어 대구 고성점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>seol_hair_@naver.com</t>
+          <t>golbange83@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1409-8331</t>
+          <t>0507-1371-2389</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 100 상가동 1층 120호</t>
+          <t>대구광역시 북구 고성로34길 69 1층 어레브헤어 대구 고성점</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/imtaejeong</t>
+          <t>https://blog.naver.com/golbange83</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3143,7 +3131,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3163,13 +3151,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>675</v>
+        <v>1940</v>
       </c>
       <c r="Q29" t="n">
-        <v>67</v>
+        <v>223</v>
       </c>
       <c r="R29" t="n">
-        <v>742</v>
+        <v>2163</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3178,12 +3166,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>13319661</t>
+          <t>1768754785</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13319661</t>
+          <t>https://m.place.naver.com/place/1768754785</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3200,29 +3188,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>더반하다헤어살롱</t>
+          <t>설헤어</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>bomi0306@naver.com</t>
+          <t>seol_hair_@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1344-1319</t>
+          <t>0507-1409-8331</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>대구광역시 북구 구암로 140 2층</t>
+          <t>대구광역시 북구 침산로 100 상가동 1층 120호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/the_banhada__</t>
+          <t>https://www.instagram.com/imtaejeong</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3257,13 +3245,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1649</v>
+        <v>675</v>
       </c>
       <c r="Q30" t="n">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="R30" t="n">
-        <v>1688</v>
+        <v>742</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3272,12 +3260,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1268688700</t>
+          <t>13319661</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1268688700</t>
+          <t>https://m.place.naver.com/place/13319661</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3294,29 +3282,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>아이드블랑 침산점</t>
+          <t>더반하다헤어살롱</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>bysoobin@naver.com</t>
+          <t>bomi0306@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1416-0812</t>
+          <t>0507-1344-1319</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 154 2층 아이드블랑</t>
+          <t>대구광역시 북구 구암로 140 2층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://instagram.com/iedeblanc_dg</t>
+          <t>https://www.instagram.com/the_banhada__</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3351,13 +3339,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>6128</v>
+        <v>1649</v>
       </c>
       <c r="Q31" t="n">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="R31" t="n">
-        <v>6230</v>
+        <v>1688</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3366,12 +3354,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1526006014</t>
+          <t>1268688700</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1526006014</t>
+          <t>https://m.place.naver.com/place/1268688700</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3388,29 +3376,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>하우룸헤어</t>
+          <t>아이드블랑 침산점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>haurumhair@naver.com</t>
+          <t>bysoobin@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1431-9925</t>
+          <t>0507-1416-0812</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>대구광역시 북구 영송로 36 1층 B102호</t>
+          <t>대구광역시 북구 침산로 154 2층 아이드블랑</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/haurumhair</t>
+          <t>http://instagram.com/iedeblanc_dg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3425,7 +3413,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3445,13 +3433,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>628</v>
+        <v>6128</v>
       </c>
       <c r="Q32" t="n">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="R32" t="n">
-        <v>643</v>
+        <v>6230</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3460,12 +3448,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1270096497</t>
+          <t>1526006014</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1270096497</t>
+          <t>https://m.place.naver.com/place/1526006014</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3482,29 +3470,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>그리나헤어</t>
+          <t>하우룸헤어</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>sadfool1@naver.com</t>
+          <t>haurumhair@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1350-6466</t>
+          <t>0507-1431-9925</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 241 아이파크상가 1층 108-3호</t>
+          <t>대구광역시 북구 영송로 36 1층 B102호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sadfool1</t>
+          <t>https://blog.naver.com/haurumhair</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3535,17 +3523,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>895</v>
+        <v>628</v>
       </c>
       <c r="Q33" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R33" t="n">
-        <v>915</v>
+        <v>643</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3554,12 +3542,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1640739218</t>
+          <t>1270096497</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1640739218</t>
+          <t>https://m.place.naver.com/place/1270096497</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3576,29 +3564,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>리업 연경점</t>
+          <t>그리나헤어</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>sujung4628@naver.com</t>
+          <t>sadfool1@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1496-2285</t>
+          <t>0507-1350-6466</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>대구광역시 북구 연경중앙로3길 21 라온하제 204호 RE:UP</t>
+          <t>대구광역시 북구 동북로 241 아이파크상가 1층 108-3호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/sadfool1</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3608,12 +3596,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3633,13 +3621,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1944</v>
+        <v>895</v>
       </c>
       <c r="Q34" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="R34" t="n">
-        <v>1947</v>
+        <v>915</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3648,12 +3636,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1612602386</t>
+          <t>1640739218</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1612602386</t>
+          <t>https://m.place.naver.com/place/1640739218</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3670,29 +3658,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>카라헤어</t>
+          <t>리업 연경점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>sungunbill@naver.com</t>
+          <t>sujung4628@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1371-2685</t>
+          <t>0507-1496-2285</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 168 201호</t>
+          <t>대구광역시 북구 연경중앙로3길 21 라온하제 204호 RE:UP</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sungunbi</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3702,7 +3690,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3723,17 +3711,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>116</v>
+        <v>1944</v>
       </c>
       <c r="Q35" t="n">
-        <v>113</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>229</v>
+        <v>1947</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3742,12 +3730,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>16061773</t>
+          <t>1612602386</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16061773</t>
+          <t>https://m.place.naver.com/place/1612602386</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3764,29 +3752,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>노블레스 헤어디자이너스 그룹</t>
+          <t>카라헤어</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>phoo5300@naver.com</t>
+          <t>sungunbill@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1428-4567</t>
+          <t>0507-1371-2685</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>대구광역시 북구 구암로 146 2층 노블레스미용실 (지상철3호선 칠곡운암역 하차)</t>
+          <t>대구광역시 북구 침산로 168 201호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/phoo5300</t>
+          <t>https://www.instagram.com/sungunbi</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3801,7 +3789,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3821,13 +3809,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3119</v>
+        <v>116</v>
       </c>
       <c r="Q36" t="n">
-        <v>2398</v>
+        <v>113</v>
       </c>
       <c r="R36" t="n">
-        <v>5517</v>
+        <v>229</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3836,12 +3824,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>20327286</t>
+          <t>16061773</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20327286</t>
+          <t>https://m.place.naver.com/place/16061773</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3858,29 +3846,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>이소프헤어</t>
+          <t>노블레스 헤어디자이너스 그룹</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>hyun_0918_@naver.com</t>
+          <t>phoo5300@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1364-9260</t>
+          <t>0507-1428-4567</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠성남로 100 301동 1층 107호</t>
+          <t>대구광역시 북구 구암로 146 2층 노블레스미용실 (지상철3호선 칠곡운암역 하차)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/isorp_smj</t>
+          <t>https://blog.naver.com/phoo5300</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3895,7 +3883,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3915,13 +3903,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>586</v>
+        <v>3119</v>
       </c>
       <c r="Q37" t="n">
-        <v>9</v>
+        <v>2398</v>
       </c>
       <c r="R37" t="n">
-        <v>595</v>
+        <v>5517</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3930,12 +3918,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1120356160</t>
+          <t>20327286</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1120356160</t>
+          <t>https://m.place.naver.com/place/20327286</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3952,29 +3940,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>리턴헤어</t>
+          <t>퍼블리헤어</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>yszin@naver.com</t>
+          <t>yuwa12@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>053-325-0180</t>
+          <t>0507-1449-2722</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>대구광역시 북구 영송로 4 1층 103호</t>
+          <t>대구광역시 북구 연경중앙로4길 17 1층 102호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/return__hair?igsh=bXhsanp4dTVibjBk&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/purvelyxx.l?igsh=MWhvdHhqdXh3ZWgydQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4009,13 +3997,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>140</v>
+        <v>292</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R38" t="n">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4024,12 +4012,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>2079859171</t>
+          <t>1555558748</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2079859171</t>
+          <t>https://m.place.naver.com/place/1555558748</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4046,29 +4034,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>헤어코드</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>haircode_@naver.com</t>
-        </is>
-      </c>
+          <t>리턴헤어</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>053-323-4974</t>
+          <t>053-325-0180</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 422 2층 헤어코드</t>
+          <t>대구광역시 북구 영송로 4 1층 103호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/haircode_</t>
+          <t>https://www.instagram.com/return__hair?igsh=bXhsanp4dTVibjBk&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4083,7 +4067,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4103,13 +4087,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>822</v>
+        <v>140</v>
       </c>
       <c r="Q39" t="n">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>909</v>
+        <v>141</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4118,12 +4102,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1707753705</t>
+          <t>2079859171</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1707753705</t>
+          <t>https://m.place.naver.com/place/2079859171</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4140,39 +4124,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>모이모이 산격점</t>
+          <t>이소프헤어</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ms9735@naver.com</t>
+          <t>hyun_0918_@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1444-5991</t>
+          <t>0507-1364-9260</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 168 2층 모이모이산격점</t>
+          <t>대구광역시 북구 칠성남로 100 301동 1층 107호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/</t>
+          <t>http://www.instagram.com/isorp_smj</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4197,13 +4181,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1787</v>
+        <v>586</v>
       </c>
       <c r="Q40" t="n">
-        <v>617</v>
+        <v>9</v>
       </c>
       <c r="R40" t="n">
-        <v>2404</v>
+        <v>595</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4212,12 +4196,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>16131608</t>
+          <t>1120356160</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16131608</t>
+          <t>https://m.place.naver.com/place/1120356160</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4234,29 +4218,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>VIP샵</t>
+          <t>헤어코드</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>lg-bestshop@naver.com</t>
+          <t>haircode_@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1453-6890</t>
+          <t>053-323-4974</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>대구광역시 북구 매전로4길 41 1층 9호, 10호</t>
+          <t>대구광역시 북구 학정로 422 2층 헤어코드</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/haircode_</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4266,12 +4250,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4287,17 +4271,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>810</v>
+        <v>823</v>
       </c>
       <c r="Q41" t="n">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="R41" t="n">
-        <v>832</v>
+        <v>910</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4306,12 +4290,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1840119765</t>
+          <t>1707753705</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1840119765</t>
+          <t>https://m.place.naver.com/place/1707753705</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4328,44 +4312,44 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>살롱물들다헤어 북구침산점</t>
+          <t>모이모이 산격점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>jung0543@naver.com</t>
+          <t>ms9735@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1310-1142</t>
+          <t>0507-1444-5991</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>대구광역시 북구 옥산로 95 3층 202호</t>
+          <t>대구광역시 북구 동북로 168 2층 모이모이산격점</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jung0543</t>
+          <t>https://booking.naver.com/</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4385,13 +4369,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3018</v>
+        <v>1787</v>
       </c>
       <c r="Q42" t="n">
-        <v>796</v>
+        <v>617</v>
       </c>
       <c r="R42" t="n">
-        <v>3814</v>
+        <v>2404</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4400,12 +4384,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1379253752</t>
+          <t>16131608</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1379253752</t>
+          <t>https://m.place.naver.com/place/16131608</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4422,29 +4406,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>살롱드보떼 침산점</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>rlagpfks7455@naver.com</t>
-        </is>
-      </c>
+          <t>VIP샵</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1377-4484</t>
+          <t>0507-1453-6890</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 166-26 2층 202호</t>
+          <t>대구광역시 북구 매전로4길 41 1층 9호, 10호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rlagpfks7455</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4454,12 +4434,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4475,17 +4455,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>286</v>
+        <v>810</v>
       </c>
       <c r="Q43" t="n">
-        <v>183</v>
+        <v>22</v>
       </c>
       <c r="R43" t="n">
-        <v>469</v>
+        <v>832</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4494,12 +4474,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1447535636</t>
+          <t>1840119765</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1447535636</t>
+          <t>https://m.place.naver.com/place/1840119765</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4516,29 +4496,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>두쏠헤어 홈플러스 칠곡점</t>
+          <t>살롱물들다헤어 북구침산점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>dusolhair0421@naver.com</t>
+          <t>jung0543@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1351-8892</t>
+          <t>0507-1310-1142</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동암로12길 8 2층 두쏠헤어</t>
+          <t>대구광역시 북구 옥산로 95 3층 202호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dusolhair0421/222855162394</t>
+          <t>https://blog.naver.com/jung0543</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4573,13 +4553,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1067</v>
+        <v>3018</v>
       </c>
       <c r="Q44" t="n">
-        <v>9</v>
+        <v>796</v>
       </c>
       <c r="R44" t="n">
-        <v>1076</v>
+        <v>3814</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4588,12 +4568,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1616556254</t>
+          <t>1379253752</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1616556254</t>
+          <t>https://m.place.naver.com/place/1379253752</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4610,29 +4590,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10.5샵</t>
+          <t>살롱드보떼 침산점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>snrkqhk7@naver.com</t>
+          <t>rlagpfks7455@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1304-2549</t>
+          <t>0507-1377-4484</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로 125-15 2층 10.5샵</t>
+          <t>대구광역시 북구 침산로 166-26 2층 202호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/10.5_hair</t>
+          <t>https://blog.naver.com/rlagpfks7455</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4647,7 +4627,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4667,13 +4647,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>191</v>
+        <v>286</v>
       </c>
       <c r="Q45" t="n">
-        <v>20</v>
+        <v>183</v>
       </c>
       <c r="R45" t="n">
-        <v>211</v>
+        <v>469</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4682,12 +4662,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1061345746</t>
+          <t>1447535636</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1061345746</t>
+          <t>https://m.place.naver.com/place/1447535636</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4704,29 +4684,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>온플리크</t>
+          <t>10.5샵</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>meang_ej@naver.com</t>
+          <t>snrkqhk7@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1313-1543</t>
+          <t>0507-1304-2549</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>대구광역시 북구 연경지묘로 8 금강프라자 2층</t>
+          <t>대구광역시 북구 동천로 125-15 2층 10.5샵</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/10.5_hair</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4736,7 +4716,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4757,17 +4737,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1813</v>
+        <v>191</v>
       </c>
       <c r="Q46" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="R46" t="n">
-        <v>1842</v>
+        <v>211</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4776,12 +4756,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1814010841</t>
+          <t>1061345746</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1814010841</t>
+          <t>https://m.place.naver.com/place/1061345746</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4798,29 +4778,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>오시리아살롱</t>
+          <t>두쏠헤어 홈플러스 칠곡점</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>tpto2002@naver.com</t>
+          <t>dusolhair0421@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1326-4338</t>
+          <t>0507-1351-8892</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대현남로6길 20 상가 307동 114호, 115호</t>
+          <t>대구광역시 북구 동암로12길 8 2층 두쏠헤어</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tpto2002</t>
+          <t>https://blog.naver.com/dusolhair0421/222855162394</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4855,13 +4835,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>350</v>
+        <v>1067</v>
       </c>
       <c r="Q47" t="n">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="R47" t="n">
-        <v>452</v>
+        <v>1076</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4870,12 +4850,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1093935512</t>
+          <t>1616556254</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1093935512</t>
+          <t>https://m.place.naver.com/place/1616556254</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4892,29 +4872,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>퀸헤어</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>korea20027@naver.com</t>
-        </is>
-      </c>
+          <t>수미살롱 침산점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>053-325-0003</t>
+          <t>0507-1350-3680</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>대구광역시 북구 태암남로 11 1층</t>
+          <t>대구광역시 북구 침산로 162-13 1층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/queenhairdaegu</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4924,7 +4900,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4945,17 +4921,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>747</v>
+        <v>125</v>
       </c>
       <c r="Q48" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="R48" t="n">
-        <v>783</v>
+        <v>155</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4964,12 +4940,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1676113740</t>
+          <t>1723688927</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1676113740</t>
+          <t>https://m.place.naver.com/place/1723688927</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4986,29 +4962,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>아라헤어</t>
+          <t>온플리크</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>arahair1002@naver.com</t>
+          <t>meang_ej@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1497-1491</t>
+          <t>0507-1313-1543</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>대구광역시 북구 내곡로 36 대성프라자 104호</t>
+          <t>대구광역시 북구 연경지묘로 8 금강프라자 2층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://arahair1002</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5018,7 +4994,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5043,13 +5019,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1087</v>
+        <v>1813</v>
       </c>
       <c r="Q49" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="R49" t="n">
-        <v>1108</v>
+        <v>1842</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5058,12 +5034,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1227408453</t>
+          <t>1814010841</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1227408453</t>
+          <t>https://m.place.naver.com/place/1814010841</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5080,29 +5056,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>유니드헤어 침산점</t>
+          <t>오시리아살롱</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>pmklove17@naver.com</t>
+          <t>tpto2002@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>053-355-2343</t>
+          <t>0507-1326-4338</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 168 엠브로타워 111호 유니드헤어</t>
+          <t>대구광역시 북구 대현남로6길 20 상가 307동 114호, 115호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/tpto2002</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5112,12 +5088,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5133,17 +5109,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>682</v>
+        <v>350</v>
       </c>
       <c r="Q50" t="n">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="R50" t="n">
-        <v>824</v>
+        <v>452</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5152,12 +5128,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1167590454</t>
+          <t>1093935512</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1167590454</t>
+          <t>https://m.place.naver.com/place/1093935512</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5174,29 +5150,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>더봄헤어</t>
+          <t>퀸헤어</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>aldiwnth@naver.com</t>
+          <t>ouou1771@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1350-9283</t>
+          <t>053-325-0003</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로106길 18</t>
+          <t>대구광역시 북구 태암남로 11 1층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/queenhairdaegu</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5206,7 +5182,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5227,17 +5203,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>148</v>
+        <v>747</v>
       </c>
       <c r="Q51" t="n">
-        <v>141</v>
+        <v>36</v>
       </c>
       <c r="R51" t="n">
-        <v>289</v>
+        <v>783</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5246,12 +5222,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>36947687</t>
+          <t>1676113740</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36947687</t>
+          <t>https://m.place.naver.com/place/1676113740</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5268,29 +5244,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>데이 미 헤어</t>
+          <t>아라헤어</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>yhj2993@naver.com</t>
+          <t>arahair1002@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>070-8985-8268</t>
+          <t>0507-1497-1491</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동화천로59길 12 1층 데이미헤어</t>
+          <t>대구광역시 북구 내곡로 36 대성프라자 104호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://arahair1002</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5300,7 +5276,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5325,13 +5301,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>395</v>
+        <v>1088</v>
       </c>
       <c r="Q52" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="R52" t="n">
-        <v>442</v>
+        <v>1109</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5340,12 +5316,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1467230508</t>
+          <t>1227408453</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1467230508</t>
+          <t>https://m.place.naver.com/place/1227408453</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5362,29 +5338,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>이프헤어</t>
+          <t>유니드헤어 침산점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ifjaemin1021@naver.com</t>
+          <t>pmklove17@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1419-2022</t>
+          <t>053-355-2343</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>대구광역시 북구 매전로4길 31 한신더휴 이스턴팰리스 402동209호</t>
+          <t>대구광역시 북구 침산로 168 엠브로타워 111호 유니드헤어</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ifjaemin1021</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5394,12 +5370,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5419,13 +5395,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1984</v>
+        <v>682</v>
       </c>
       <c r="Q53" t="n">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="R53" t="n">
-        <v>2086</v>
+        <v>824</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5434,12 +5410,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>38495146</t>
+          <t>1167590454</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38495146</t>
+          <t>https://m.place.naver.com/place/1167590454</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5456,29 +5432,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>프로뮤헤어</t>
+          <t>더봄헤어</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>neenaa@naver.com</t>
+          <t>plaire1113@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1445-2128</t>
+          <t>0507-1350-9283</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 140 3층 301호</t>
+          <t>대구광역시 북구 학정로106길 18</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/neenaa</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5488,12 +5464,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5509,17 +5485,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>5220</v>
+        <v>148</v>
       </c>
       <c r="Q54" t="n">
-        <v>309</v>
+        <v>141</v>
       </c>
       <c r="R54" t="n">
-        <v>5529</v>
+        <v>289</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5528,12 +5504,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1102048730</t>
+          <t>36947687</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1102048730</t>
+          <t>https://m.place.naver.com/place/36947687</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5550,29 +5526,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>라스텔라</t>
+          <t>데이 미 헤어</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>dls3456@naver.com</t>
+          <t>yhj2993@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1436-6669</t>
+          <t>070-8985-8268</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로 132 203호 라스텔라</t>
+          <t>대구광역시 북구 동화천로59길 12 1층 데이미헤어</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dls3456</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5582,12 +5558,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5607,13 +5583,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>7872</v>
+        <v>395</v>
       </c>
       <c r="Q55" t="n">
-        <v>147</v>
+        <v>47</v>
       </c>
       <c r="R55" t="n">
-        <v>8019</v>
+        <v>442</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5622,12 +5598,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>34321487</t>
+          <t>1467230508</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34321487</t>
+          <t>https://m.place.naver.com/place/1467230508</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5644,34 +5620,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>부래미헤어 산격점</t>
+          <t>이프헤어</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>booraemi_hair@naver.com</t>
+          <t>ifjaemin1021@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1438-1297</t>
+          <t>0507-1419-2022</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대학로 145 1층 부래미헤어산격점</t>
+          <t>대구광역시 북구 매전로4길 31 한신더휴 이스턴팰리스 402동209호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/profile/c/booraemi_sg</t>
+          <t>https://blog.naver.com/ifjaemin1021</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5681,19 +5657,15 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/profile</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>X</t>
@@ -5701,17 +5673,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>10004</v>
+        <v>1984</v>
       </c>
       <c r="Q56" t="n">
-        <v>882</v>
+        <v>102</v>
       </c>
       <c r="R56" t="n">
-        <v>10886</v>
+        <v>2086</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5720,12 +5692,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>38376779</t>
+          <t>38495146</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38376779</t>
+          <t>https://m.place.naver.com/place/38495146</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5742,29 +5714,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>민트 헤어</t>
+          <t>프로뮤헤어</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>loveyourself_@naver.com</t>
+          <t>neenaa@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>053-311-4783</t>
+          <t>0507-1445-2128</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>대구광역시 북구 도남중앙로7길 20-10 2층 205호</t>
+          <t>대구광역시 북구 침산남로 140 3층 301호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/neenaa</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5774,12 +5746,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5795,17 +5767,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>275</v>
+        <v>5220</v>
       </c>
       <c r="Q57" t="n">
-        <v>8</v>
+        <v>309</v>
       </c>
       <c r="R57" t="n">
-        <v>283</v>
+        <v>5529</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5814,12 +5786,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1618672546</t>
+          <t>1102048730</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1618672546</t>
+          <t>https://m.place.naver.com/place/1102048730</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5836,29 +5808,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>브넬헤어 경북대북문점</t>
+          <t>라스텔라</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>yuseonghun@naver.com</t>
+          <t>dls3456@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1460-2363</t>
+          <t>0507-1436-6669</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대학로 63 3층</t>
+          <t>대구광역시 북구 동천로 132 203호 라스텔라</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/dls3456</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5868,12 +5840,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5893,13 +5865,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1403</v>
+        <v>7874</v>
       </c>
       <c r="Q58" t="n">
-        <v>26</v>
+        <v>147</v>
       </c>
       <c r="R58" t="n">
-        <v>1429</v>
+        <v>8021</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5908,12 +5880,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1654118317</t>
+          <t>34321487</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1654118317</t>
+          <t>https://m.place.naver.com/place/34321487</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5930,30 +5902,34 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>머리할때됐다 칠곡점</t>
+          <t>부래미헤어 산격점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>itstime_hair@naver.com</t>
+          <t>booraemi_hair@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1438-1297</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔거천동로34길 16-19</t>
+          <t>대구광역시 북구 대학로 145 1층 부래미헤어산격점</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/itstime_hair</t>
+          <t>https://talk.naver.com/profile/c/booraemi_sg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5963,15 +5939,19 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/profile</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr">
         <is>
           <t>X</t>
@@ -5979,17 +5959,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>90</v>
+        <v>10008</v>
       </c>
       <c r="Q59" t="n">
-        <v>27</v>
+        <v>883</v>
       </c>
       <c r="R59" t="n">
-        <v>117</v>
+        <v>10891</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5998,12 +5978,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1029214736</t>
+          <t>38376779</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1029214736</t>
+          <t>https://m.place.naver.com/place/38376779</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6020,29 +6000,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>라츠헤어 복현점</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>aa00kmr@naver.com</t>
-        </is>
-      </c>
+          <t>브넬헤어 경북대북문점</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1403-3779</t>
+          <t>0507-1460-2363</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>대구광역시 북구 공항로 11 2층</t>
+          <t>대구광역시 북구 대학로 63 3층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lots_hair/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6052,7 +6028,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6073,17 +6049,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>7391</v>
+        <v>1404</v>
       </c>
       <c r="Q60" t="n">
-        <v>106</v>
+        <v>26</v>
       </c>
       <c r="R60" t="n">
-        <v>7497</v>
+        <v>1430</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6092,12 +6068,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>37157753</t>
+          <t>1654118317</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37157753</t>
+          <t>https://m.place.naver.com/place/1654118317</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6114,29 +6090,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>살롱드수장</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>thssksfh12@naver.com</t>
-        </is>
-      </c>
+          <t>라츠헤어 복현점</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1302-1434</t>
+          <t>0507-1403-3779</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠성남로 30 대구역오페라힐스테이트 상가 108호</t>
+          <t>대구광역시 북구 공항로 11 2층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/salon_de_sujang</t>
+          <t>https://www.instagram.com/lots_hair/</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6171,13 +6143,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>457</v>
+        <v>7391</v>
       </c>
       <c r="Q61" t="n">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="R61" t="n">
-        <v>517</v>
+        <v>7497</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6186,12 +6158,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1460738008</t>
+          <t>37157753</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1460738008</t>
+          <t>https://m.place.naver.com/place/37157753</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6208,29 +6180,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>살롱드두 복현점</t>
+          <t>살롱드수장</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>salondedoux@naver.com</t>
+          <t>thssksfh12@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1370-8668</t>
+          <t>0507-1302-1434</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>대구광역시 북구 공항로 8 1층 살롱드두</t>
+          <t>대구광역시 북구 칠성남로 30 대구역오페라힐스테이트 상가 108호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/doux___hair</t>
+          <t>https://www.instagram.com/salon_de_sujang</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6265,13 +6237,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>890</v>
+        <v>457</v>
       </c>
       <c r="Q62" t="n">
-        <v>280</v>
+        <v>60</v>
       </c>
       <c r="R62" t="n">
-        <v>1170</v>
+        <v>517</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6280,12 +6252,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1908451460</t>
+          <t>1460738008</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1908451460</t>
+          <t>https://m.place.naver.com/place/1460738008</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6302,34 +6274,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>이쁘다헤어 침산점</t>
+          <t>살롱드두 복현점</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ippudahair@naver.com</t>
+          <t>salondedoux@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1485-0307</t>
+          <t>0507-1370-8668</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 173 3층 이쁘다헤어 침산점</t>
+          <t>대구광역시 북구 공항로 8 1층 살롱드두</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://ippudahair.com/</t>
+          <t>https://www.instagram.com/doux___hair</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6339,7 +6311,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6359,13 +6331,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1894</v>
+        <v>890</v>
       </c>
       <c r="Q63" t="n">
-        <v>494</v>
+        <v>281</v>
       </c>
       <c r="R63" t="n">
-        <v>2388</v>
+        <v>1171</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6374,12 +6346,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>2056858156</t>
+          <t>1908451460</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2056858156</t>
+          <t>https://m.place.naver.com/place/1908451460</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6396,34 +6368,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>리베르헤어</t>
+          <t>이쁘다헤어 침산점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>cpfl352@naver.com</t>
+          <t>ippudahair@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1381-9963</t>
+          <t>0507-1485-0307</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>대구광역시 북구 노원로10길 40 노원한신더휴 아파트상가 102호</t>
+          <t>대구광역시 북구 침산로 173 3층 이쁘다헤어 침산점</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cpfl352</t>
+          <t>https://ippudahair.com/</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6453,13 +6425,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>614</v>
+        <v>1894</v>
       </c>
       <c r="Q64" t="n">
-        <v>35</v>
+        <v>495</v>
       </c>
       <c r="R64" t="n">
-        <v>649</v>
+        <v>2389</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6468,12 +6440,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1162963087</t>
+          <t>2056858156</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1162963087</t>
+          <t>https://m.place.naver.com/place/2056858156</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6493,11 +6465,7 @@
           <t>더봄헤어</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>aldiwnth@naver.com</t>
-        </is>
-      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
@@ -6611,7 +6579,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7017,13 +6985,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>4287</v>
+        <v>4288</v>
       </c>
       <c r="Q70" t="n">
         <v>236</v>
       </c>
       <c r="R70" t="n">
-        <v>4523</v>
+        <v>4524</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7151,11 +7119,7 @@
           <t>세없결 대구침산점</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>casual5908@naver.com</t>
-        </is>
-      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
@@ -7245,11 +7209,7 @@
           <t>더 덴 바버샵</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>hsohlily123@naver.com</t>
-        </is>
-      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
@@ -7581,13 +7541,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="Q76" t="n">
         <v>308</v>
       </c>
       <c r="R76" t="n">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
